--- a/AAII_Financials/Quarterly/KVUE_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/KVUE_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="92">
   <si>
     <t>KVUE</t>
   </si>
@@ -656,95 +656,96 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:X102"/>
+  <dimension ref="A5:Y102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="24" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="25" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46201</v>
+      </c>
+      <c r="E7" s="2">
         <v>46110</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46019</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45928</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45837</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45746</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45655</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45564</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45200</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45109</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45018</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44927</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44836</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44745</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44472</v>
       </c>
-      <c r="U7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V7" s="2" t="s">
         <v>3</v>
       </c>
@@ -754,65 +755,68 @@
       <c r="X7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>3955000</v>
+      </c>
+      <c r="E8" s="3">
         <v>3909000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>3780000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>3764000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>3839000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>3741000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>3662000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>3899000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>4000000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3894000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>3666000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>3915000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>4011000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>3852000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>3767000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>3789000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>3804000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>11321000</v>
       </c>
-      <c r="U8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V8" s="3" t="s">
         <v>3</v>
       </c>
@@ -822,65 +826,68 @@
       <c r="X8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>1645000</v>
+      </c>
+      <c r="E9" s="3">
         <v>1602000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1627000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1530000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1572000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1567000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1584000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1613000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1626000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1646000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1623000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1665000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1786000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1727000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1661000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1637000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1646000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>4851000</v>
       </c>
-      <c r="U9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V9" s="3" t="s">
         <v>3</v>
       </c>
@@ -890,65 +897,68 @@
       <c r="X9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>2310000</v>
+      </c>
+      <c r="E10" s="3">
         <v>2307000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>2153000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>2234000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>2267000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>2174000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>2078000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>2286000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2374000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>2248000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>2043000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>2250000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>2225000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>2125000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>2106000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>2152000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>2158000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>6470000</v>
       </c>
-      <c r="U10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V10" s="3" t="s">
         <v>3</v>
       </c>
@@ -958,8 +968,11 @@
       <c r="X10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -984,65 +997,66 @@
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y11" s="3"/>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>94000</v>
+      </c>
+      <c r="E12" s="3">
         <v>84000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>98000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>94000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>91000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>99000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>106000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>97000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>105000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>100000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>133000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>78000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>99000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>89000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>103000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>90000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>94000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>253000</v>
       </c>
-      <c r="U12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1052,8 +1066,11 @@
       <c r="X12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1120,65 +1137,68 @@
       <c r="X13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>69000</v>
+      </c>
+      <c r="E14" s="3">
         <v>78000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>147000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>97000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>68000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>67000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>105000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>38000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>568000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>149000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>392000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-6000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>-22000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>-2000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>205000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>63000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>-10000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>102000</v>
       </c>
-      <c r="U14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1188,53 +1208,56 @@
       <c r="X14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>145000</v>
+      </c>
+      <c r="E15" s="3">
         <v>143000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>39000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>141000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>142000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>136000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>5000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>182000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>141000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>149000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>174000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>153000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>148000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>152000</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
       <c r="R15" s="3">
         <v>0</v>
       </c>
@@ -1256,8 +1279,11 @@
       <c r="X15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1279,65 +1305,66 @@
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
-    </row>
-    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y16" s="3"/>
+    </row>
+    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>3187000</v>
+      </c>
+      <c r="E17" s="3">
         <v>3064000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>3106000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>3038000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>3079000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>3116000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>3097000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>3207000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>3278000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>3226000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2832000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>3202000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>3331000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>3221000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>3236000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>3026000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>3024000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>8898000</v>
       </c>
-      <c r="U17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1347,65 +1374,68 @@
       <c r="X17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>768000</v>
+      </c>
+      <c r="E18" s="3">
         <v>845000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>674000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>726000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>760000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>625000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>565000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>692000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>722000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>668000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>834000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>713000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>680000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>631000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>531000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>763000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>780000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>2423000</v>
       </c>
-      <c r="U18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1415,8 +1445,11 @@
       <c r="X18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1441,65 +1474,66 @@
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
-    </row>
-    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y19" s="3"/>
+    </row>
+    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E20" s="3">
+      <c r="D20" s="3">
+        <v>11000</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F20" s="3">
         <v>2000</v>
-      </c>
-      <c r="F20" s="3">
-        <v>10000</v>
       </c>
       <c r="G20" s="3">
         <v>10000</v>
       </c>
       <c r="H20" s="3">
+        <v>10000</v>
+      </c>
+      <c r="I20" s="3">
         <v>6000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>19000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-19000</v>
-      </c>
-      <c r="K20" s="3">
-        <v>-3000</v>
       </c>
       <c r="L20" s="3">
         <v>-3000</v>
       </c>
       <c r="M20" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="N20" s="3">
         <v>-11000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>34000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>10000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>23000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-19000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-25000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-5000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-15000</v>
       </c>
-      <c r="U20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1509,65 +1543,68 @@
       <c r="X20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>902000</v>
+      </c>
+      <c r="E21" s="3">
         <v>988000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>711000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>857000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>892000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>755000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>551000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>893000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>866000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>820000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1019000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>832000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>818000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>760000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>678000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>890000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>936000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>2957000</v>
       </c>
-      <c r="U21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1577,19 +1614,22 @@
       <c r="X21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>103000</v>
+      </c>
+      <c r="E22" s="3">
         <v>106000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>109000</v>
-      </c>
-      <c r="F22" s="3">
-        <v>107000</v>
       </c>
       <c r="G22" s="3">
         <v>107000</v>
@@ -1598,46 +1638,46 @@
         <v>107000</v>
       </c>
       <c r="I22" s="3">
-        <v>108000</v>
+        <v>107000</v>
       </c>
       <c r="J22" s="3">
         <v>108000</v>
       </c>
       <c r="K22" s="3">
+        <v>108000</v>
+      </c>
+      <c r="L22" s="3">
         <v>106000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>109000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>114000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>115000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>118000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>11000</v>
       </c>
-      <c r="Q22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S22" s="3">
-        <v>0</v>
-      </c>
-      <c r="T22" s="3" t="s">
-        <v>3</v>
+      <c r="S22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T22" s="3">
+        <v>0</v>
       </c>
       <c r="U22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V22" s="3">
-        <v>0</v>
+      <c r="V22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W22" s="3">
         <v>0</v>
@@ -1645,65 +1685,68 @@
       <c r="X22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>598000</v>
+      </c>
+      <c r="E23" s="3">
         <v>672000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>427000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>526000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>588000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>458000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>346000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>577000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>65000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>427000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>357000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>585000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>639000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>609000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>512000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>738000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>775000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>2408000</v>
       </c>
-      <c r="U23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1713,65 +1756,68 @@
       <c r="X23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>142000</v>
+      </c>
+      <c r="E24" s="3">
         <v>198000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>97000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>128000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>168000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>136000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>53000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>194000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>7000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>131000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>30000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>147000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>209000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>140000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>151000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>153000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>171000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>788000</v>
       </c>
-      <c r="U24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1781,8 +1827,11 @@
       <c r="X24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1849,65 +1898,68 @@
       <c r="X25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>456000</v>
+      </c>
+      <c r="E26" s="3">
         <v>474000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>330000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>398000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>420000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>322000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>293000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>383000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>58000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>296000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>327000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>438000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>430000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>469000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>361000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>585000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>604000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>1620000</v>
       </c>
-      <c r="U26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1917,65 +1969,68 @@
       <c r="X26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>456000</v>
+      </c>
+      <c r="E27" s="3">
         <v>474000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>330000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>398000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>420000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>322000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>293000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>383000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>58000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>296000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>327000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>438000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>430000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>469000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>361000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>585000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>604000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>1620000</v>
       </c>
-      <c r="U27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1985,8 +2040,11 @@
       <c r="X27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2053,8 +2111,11 @@
       <c r="X28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2121,8 +2182,11 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2189,8 +2253,11 @@
       <c r="X30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2257,65 +2324,68 @@
       <c r="X31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E32" s="3">
+      <c r="D32" s="3">
+        <v>-11000</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F32" s="3">
         <v>-2000</v>
-      </c>
-      <c r="F32" s="3">
-        <v>-10000</v>
       </c>
       <c r="G32" s="3">
         <v>-10000</v>
       </c>
       <c r="H32" s="3">
+        <v>-10000</v>
+      </c>
+      <c r="I32" s="3">
         <v>-6000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-19000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>19000</v>
-      </c>
-      <c r="K32" s="3">
-        <v>3000</v>
       </c>
       <c r="L32" s="3">
         <v>3000</v>
       </c>
       <c r="M32" s="3">
+        <v>3000</v>
+      </c>
+      <c r="N32" s="3">
         <v>11000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-34000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-10000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-23000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>19000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>25000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>5000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>15000</v>
       </c>
-      <c r="U32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2325,65 +2395,68 @@
       <c r="X32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>456000</v>
+      </c>
+      <c r="E33" s="3">
         <v>474000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>330000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>398000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>420000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>322000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>293000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>383000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>58000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>296000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>327000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>438000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>430000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>469000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>361000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>585000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>604000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>1620000</v>
       </c>
-      <c r="U33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2393,8 +2466,11 @@
       <c r="X33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2461,65 +2537,68 @@
       <c r="X34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>456000</v>
+      </c>
+      <c r="E35" s="3">
         <v>474000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>330000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>398000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>420000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>322000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>293000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>383000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>58000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>296000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>327000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>438000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>430000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>469000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>361000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>585000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>604000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>1620000</v>
       </c>
-      <c r="U35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2529,70 +2608,73 @@
       <c r="X35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46201</v>
+      </c>
+      <c r="E38" s="2">
         <v>46110</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46019</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45928</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45837</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45746</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45655</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45564</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45200</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45109</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45018</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44927</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44836</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44745</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44472</v>
       </c>
-      <c r="U38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2602,8 +2684,11 @@
       <c r="X38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2628,8 +2713,9 @@
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
-    </row>
-    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y39" s="3"/>
+    </row>
+    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2654,59 +2740,60 @@
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
-    </row>
-    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y40" s="3"/>
+    </row>
+    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1110000</v>
+      </c>
+      <c r="E41" s="3">
         <v>1075000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1062000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1139000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1070000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1057000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1070000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1057000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1014000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1155000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1382000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1062000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1231000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1691000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1231000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>797000</v>
       </c>
-      <c r="S41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2722,8 +2809,11 @@
       <c r="X41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2790,59 +2880,62 @@
       <c r="X42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2476000</v>
+      </c>
+      <c r="E43" s="3">
         <v>2501000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>2382000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>2416000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>2331000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>2312000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>2165000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2394000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2240000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2160000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2073000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2109000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2096000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>2109000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>2122000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>2141000</v>
       </c>
-      <c r="S43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2858,59 +2951,62 @@
       <c r="X43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1722000</v>
+      </c>
+      <c r="E44" s="3">
         <v>1674000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1666000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1794000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1776000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1680000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1591000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1820000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1849000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1884000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1851000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1885000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>2026000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>2222000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>2226000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>2133000</v>
       </c>
-      <c r="S44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2926,59 +3022,62 @@
       <c r="X44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>166000</v>
+      </c>
+      <c r="E45" s="3">
         <v>151000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>177000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>176000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>175000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>188000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>257000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>228000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>250000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>275000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>283000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>252000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>241000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>206000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>298000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>392000</v>
       </c>
-      <c r="S45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2994,59 +3093,62 @@
       <c r="X45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>5899000</v>
+      </c>
+      <c r="E46" s="3">
         <v>5795000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>5697000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>6032000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>5854000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>5710000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>5525000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>5941000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>5881000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>6097000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>6138000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>5894000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>6219000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>6439000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>5877000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>5463000</v>
       </c>
-      <c r="S46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3062,8 +3164,11 @@
       <c r="X46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3085,8 +3190,8 @@
       <c r="I47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J47" s="3">
-        <v>41000</v>
+      <c r="J47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K47" s="3">
         <v>41000</v>
@@ -3095,20 +3200,20 @@
         <v>41000</v>
       </c>
       <c r="M47" s="3">
+        <v>41000</v>
+      </c>
+      <c r="N47" s="3">
         <v>71000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>76000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>78000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>56000</v>
       </c>
-      <c r="Q47" s="3">
-        <v>0</v>
-      </c>
       <c r="R47" s="3">
         <v>0</v>
       </c>
@@ -3130,59 +3235,62 @@
       <c r="X47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2226000</v>
+      </c>
+      <c r="E48" s="3">
         <v>2208000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2363000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2092000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2038000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1927000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1960000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1898000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2127000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2145000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>2181000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1872000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1832000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1836000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1820000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1700000</v>
       </c>
-      <c r="S48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3198,59 +3306,62 @@
       <c r="X48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>17671000</v>
+      </c>
+      <c r="E49" s="3">
         <v>17916000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>18203000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>18157000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>18290000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>17722000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>17317000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>18184000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>17735000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>18410000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>18890000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>18461000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>18759000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>19071000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>19038000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>18315000</v>
       </c>
-      <c r="S49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3266,8 +3377,11 @@
       <c r="X49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3334,8 +3448,11 @@
       <c r="X50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3402,59 +3519,62 @@
       <c r="X51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>692000</v>
+      </c>
+      <c r="E52" s="3">
         <v>703000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>576000</v>
-      </c>
-      <c r="F52" s="3">
-        <v>730000</v>
       </c>
       <c r="G52" s="3">
         <v>730000</v>
       </c>
       <c r="H52" s="3">
+        <v>730000</v>
+      </c>
+      <c r="I52" s="3">
         <v>699000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>615000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>633000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>453000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>419000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>413000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>618000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>511000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>8025000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>581000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>544000</v>
       </c>
-      <c r="S52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3470,8 +3590,11 @@
       <c r="X52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3538,59 +3661,62 @@
       <c r="X53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>26735000</v>
+      </c>
+      <c r="E54" s="3">
         <v>26854000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>27076000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>27248000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>27132000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>26257000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>25601000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>26925000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>26443000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>27283000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>27851000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>27077000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>27542000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>35595000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>27316000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>26022000</v>
       </c>
-      <c r="S54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3606,8 +3732,11 @@
       <c r="X54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3632,8 +3761,9 @@
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
-    </row>
-    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y55" s="3"/>
+    </row>
+    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3658,59 +3788,60 @@
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
-    </row>
-    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y56" s="3"/>
+    </row>
+    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2577000</v>
+      </c>
+      <c r="E57" s="3">
         <v>2533000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2473000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2445000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2568000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2332000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2254000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2274000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2437000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2602000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2489000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2281000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2354000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1781000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1829000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1745000</v>
       </c>
-      <c r="S57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3726,53 +3857,56 @@
       <c r="X57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1447000</v>
+      </c>
+      <c r="E58" s="3">
         <v>1631000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1496000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1951000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1591000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>2466000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1588000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1688000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1467000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1566000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>643000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>559000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>799000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>32000</v>
       </c>
-      <c r="Q58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3785,8 +3919,8 @@
       <c r="U58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V58" s="3">
-        <v>0</v>
+      <c r="V58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W58" s="3">
         <v>0</v>
@@ -3794,59 +3928,62 @@
       <c r="X58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>127000</v>
+        <v>91000</v>
       </c>
       <c r="E59" s="3">
         <v>127000</v>
       </c>
       <c r="F59" s="3">
+        <v>127000</v>
+      </c>
+      <c r="G59" s="3">
         <v>126000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>142000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>236000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>156000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>249000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>272000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>334000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>255000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>383000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>239000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>604000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>2097000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>2122000</v>
       </c>
-      <c r="S59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3862,59 +3999,62 @@
       <c r="X59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>5867000</v>
+      </c>
+      <c r="E60" s="3">
         <v>5896000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>5945000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>6156000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>5988000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>6666000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>5739000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>5946000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>5937000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>6166000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>5481000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>5161000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>5299000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>4210000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>3926000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>3867000</v>
       </c>
-      <c r="S60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3930,53 +4070,56 @@
       <c r="X60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>7166000</v>
+      </c>
+      <c r="E61" s="3">
         <v>7171000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>7178000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>7158000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>7153000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>6385000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>7131000</v>
-      </c>
-      <c r="J61" s="3">
-        <v>7139000</v>
       </c>
       <c r="K61" s="3">
         <v>7139000</v>
       </c>
       <c r="L61" s="3">
+        <v>7139000</v>
+      </c>
+      <c r="M61" s="3">
         <v>7131000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>7784000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>7791000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>7804000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>7761000</v>
       </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
       <c r="R61" s="3">
         <v>0</v>
       </c>
@@ -3998,8 +4141,11 @@
       <c r="X61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4007,50 +4153,50 @@
         <v>480000</v>
       </c>
       <c r="E62" s="3">
+        <v>480000</v>
+      </c>
+      <c r="F62" s="3">
         <v>494000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>502000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>510000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>483000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>460000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>456000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>447000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>443000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>394000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>463000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>473000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>431000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>3369000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>3228000</v>
       </c>
-      <c r="S62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4066,8 +4212,11 @@
       <c r="X62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4134,8 +4283,11 @@
       <c r="X63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4202,8 +4354,11 @@
       <c r="X64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4270,59 +4425,62 @@
       <c r="X65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>16182000</v>
+      </c>
+      <c r="E66" s="3">
         <v>16246000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>16311000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>16614000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>16402000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>16204000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>15933000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>16281000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>16265000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>16662000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>16640000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>16184000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>16502000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>15313000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>7295000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>7095000</v>
       </c>
-      <c r="S66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4338,8 +4496,11 @@
       <c r="X66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4364,8 +4525,9 @@
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
-    </row>
-    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y67" s="3"/>
+    </row>
+    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4432,8 +4594,11 @@
       <c r="X68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4500,8 +4665,11 @@
       <c r="X69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4568,8 +4736,11 @@
       <c r="X70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4636,59 +4807,62 @@
       <c r="X71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-70000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-128000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-204000</v>
-      </c>
-      <c r="F72" s="3">
-        <v>-136000</v>
       </c>
       <c r="G72" s="3">
         <v>-136000</v>
       </c>
       <c r="H72" s="3">
+        <v>-136000</v>
+      </c>
+      <c r="I72" s="3">
         <v>-163000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-93000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>7000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>17000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>342000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>429000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>485000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>430000</v>
       </c>
-      <c r="P72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q72" s="3">
+      <c r="Q72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R72" s="3">
         <v>25474000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>25153000</v>
       </c>
-      <c r="S72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4704,8 +4878,11 @@
       <c r="X72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4772,8 +4949,11 @@
       <c r="X73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4840,8 +5020,11 @@
       <c r="X74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4908,59 +5091,62 @@
       <c r="X75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>10553000</v>
+      </c>
+      <c r="E76" s="3">
         <v>10608000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>10765000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>10634000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>10730000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>10053000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>9668000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>10644000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>10178000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>10621000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>11211000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>10893000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>11040000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>20282000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>20021000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>18927000</v>
       </c>
-      <c r="S76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4976,8 +5162,11 @@
       <c r="X76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5044,70 +5233,73 @@
       <c r="X77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46201</v>
+      </c>
+      <c r="E80" s="2">
         <v>46110</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46019</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45928</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45837</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45746</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45655</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45564</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45200</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45109</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45018</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44927</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44836</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44745</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44472</v>
       </c>
-      <c r="U80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V80" s="2" t="s">
         <v>3</v>
       </c>
@@ -5117,65 +5309,68 @@
       <c r="X80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>456000</v>
+      </c>
+      <c r="E81" s="3">
         <v>474000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>330000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>398000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>420000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>322000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>293000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>383000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>58000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>296000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>327000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>438000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>430000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>469000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>361000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>585000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>604000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>1620000</v>
       </c>
-      <c r="U81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V81" s="3" t="s">
         <v>3</v>
       </c>
@@ -5185,8 +5380,11 @@
       <c r="X81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5211,62 +5409,63 @@
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
-    </row>
-    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y82" s="3"/>
+    </row>
+    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>78000</v>
+      </c>
+      <c r="E83" s="3">
         <v>73000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>5000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>116000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>69000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>75000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>94000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>71000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>69000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>71000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>83000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>69000</v>
-      </c>
-      <c r="O83" s="3">
-        <v>72000</v>
       </c>
       <c r="P83" s="3">
         <v>72000</v>
       </c>
       <c r="Q83" s="3">
+        <v>72000</v>
+      </c>
+      <c r="R83" s="3">
         <v>166000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>152000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>161000</v>
       </c>
-      <c r="T83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U83" s="3" t="s">
         <v>3</v>
       </c>
@@ -5279,8 +5478,11 @@
       <c r="X83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5347,8 +5549,11 @@
       <c r="X84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5415,8 +5620,11 @@
       <c r="X85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5483,8 +5691,11 @@
       <c r="X86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5551,8 +5762,11 @@
       <c r="X87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5619,62 +5833,65 @@
       <c r="X88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>688000</v>
+      </c>
+      <c r="E89" s="3">
         <v>489000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>854000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>294000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>621000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>428000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>793000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>249000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>440000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>287000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>950000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>674000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>742000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>802000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>644000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>736000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>807000</v>
       </c>
-      <c r="T89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U89" s="3" t="s">
         <v>3</v>
       </c>
@@ -5687,8 +5904,11 @@
       <c r="X89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5713,62 +5933,63 @@
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
-    </row>
-    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y90" s="3"/>
+    </row>
+    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-64000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-139000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-110000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-98000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-88000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-179000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-138000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-59000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-90000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-153000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-223000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-114000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-77000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-55000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-159000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-103000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-76000</v>
       </c>
-      <c r="T91" s="3">
-        <v>0</v>
-      </c>
       <c r="U91" s="3">
         <v>0</v>
       </c>
@@ -5781,8 +6002,11 @@
       <c r="X91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5849,8 +6073,11 @@
       <c r="X92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5917,62 +6144,65 @@
       <c r="X93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-78000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-167000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-75000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-104000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-90000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-167000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-132000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-56000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-85000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-152000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-265000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-105000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-77000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-41000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-167000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-108000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-73000</v>
       </c>
-      <c r="T94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U94" s="3" t="s">
         <v>3</v>
       </c>
@@ -5985,8 +6215,11 @@
       <c r="X94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6011,8 +6244,9 @@
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
-    </row>
-    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y95" s="3"/>
+    </row>
+    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6026,37 +6260,37 @@
         <v>398000</v>
       </c>
       <c r="G96" s="3">
+        <v>398000</v>
+      </c>
+      <c r="H96" s="3">
         <v>393000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>392000</v>
-      </c>
-      <c r="I96" s="3">
-        <v>393000</v>
       </c>
       <c r="J96" s="3">
         <v>393000</v>
       </c>
       <c r="K96" s="3">
-        <v>383000</v>
+        <v>393000</v>
       </c>
       <c r="L96" s="3">
         <v>383000</v>
       </c>
-      <c r="M96" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N96" s="3">
+      <c r="M96" s="3">
         <v>383000</v>
       </c>
+      <c r="N96" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="O96" s="3">
+        <v>383000</v>
+      </c>
+      <c r="P96" s="3">
         <v>13788000</v>
       </c>
-      <c r="P96" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q96" s="3">
-        <v>0</v>
+      <c r="Q96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R96" s="3">
         <v>0</v>
@@ -6079,8 +6313,11 @@
       <c r="X96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6147,8 +6384,11 @@
       <c r="X97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6215,8 +6455,11 @@
       <c r="X98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6283,62 +6526,65 @@
       <c r="X99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-587000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-295000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-869000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-110000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-548000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-310000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-587000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-162000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-490000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-326000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-383000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-726000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-8806000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>7388000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-63000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-635000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-675000</v>
       </c>
-      <c r="T100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U100" s="3" t="s">
         <v>3</v>
       </c>
@@ -6351,62 +6597,65 @@
       <c r="X100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>30000</v>
+      </c>
+      <c r="E101" s="3">
         <v>36000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-61000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>12000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-6000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-36000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>18000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-12000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-14000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>6000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>20000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-34000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-50000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>3000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>20000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-34000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-50000</v>
       </c>
-      <c r="T101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U101" s="3" t="s">
         <v>3</v>
       </c>
@@ -6419,62 +6668,65 @@
       <c r="X101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>35000</v>
+      </c>
+      <c r="E102" s="3">
         <v>13000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-77000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>69000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>13000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-13000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>13000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>43000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-141000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-227000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>320000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-169000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-8155000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>8155000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>434000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-41000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>9000</v>
       </c>
-      <c r="T102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U102" s="3" t="s">
         <v>3</v>
       </c>
@@ -6485,6 +6737,9 @@
         <v>3</v>
       </c>
       <c r="X102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
